--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{665BD34E-A8C5-46FC-A953-CD410197F7DF}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65941DB2-D309-4CEC-BA90-487159D740B4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="158">
   <si>
     <t>Teacher</t>
   </si>
@@ -493,9 +493,6 @@
   </si>
   <si>
     <t>12TH ARTS D+F</t>
-  </si>
-  <si>
-    <t>BABITA</t>
   </si>
   <si>
     <t>11TH SCI A(3,4)</t>
@@ -953,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -1575,7 +1572,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>103</v>
@@ -1903,7 +1900,7 @@
         <v>108</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>99</v>
@@ -1926,7 +1923,7 @@
         <v>129</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>99</v>
@@ -2156,7 +2153,7 @@
         <v>99</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>110</v>
@@ -2274,29 +2271,6 @@
         <v>99</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G58" s="1" t="s">
         <v>99</v>
       </c>
     </row>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65941DB2-D309-4CEC-BA90-487159D740B4}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{478B2D59-E87A-4D18-8954-0A1AD868EE56}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="159">
   <si>
     <t>Teacher</t>
   </si>
@@ -273,9 +273,6 @@
     <t>11TH SCI B</t>
   </si>
   <si>
-    <t>11TH SCI B(1-2)</t>
-  </si>
-  <si>
     <t>11TH SCI C</t>
   </si>
   <si>
@@ -348,15 +345,6 @@
     <t>11TH SCI B(5,6)</t>
   </si>
   <si>
-    <t>12TH SCI A(3,4)</t>
-  </si>
-  <si>
-    <t>11TH SCI C(1,2)</t>
-  </si>
-  <si>
-    <t>12TH SCI B(5,6)</t>
-  </si>
-  <si>
     <t>11TH ARTS</t>
   </si>
   <si>
@@ -390,9 +378,6 @@
     <t>11TH SCI B(3,4)                11SCI D(5,6)</t>
   </si>
   <si>
-    <t>12TH SCI B (1,2)</t>
-  </si>
-  <si>
     <t>12TH SCI A(1,2)</t>
   </si>
   <si>
@@ -432,9 +417,6 @@
     <t>11  ARTS+COMM+SCI (CS)</t>
   </si>
   <si>
-    <t xml:space="preserve">9TH (CS) </t>
-  </si>
-  <si>
     <t>10TH (CS)</t>
   </si>
   <si>
@@ -498,13 +480,34 @@
     <t>11TH SCI A(3,4)</t>
   </si>
   <si>
-    <t>11TH SCI C + ARTS B</t>
-  </si>
-  <si>
     <t xml:space="preserve">9TH </t>
   </si>
   <si>
-    <t>9TH (SKT)</t>
+    <t>12 TH SCI C</t>
+  </si>
+  <si>
+    <t>12TH SCI B (5,6)</t>
+  </si>
+  <si>
+    <t>11TH SCI C(3,4)</t>
+  </si>
+  <si>
+    <t>11TH SCI B(1,2)</t>
+  </si>
+  <si>
+    <t>12TH SCI B(1,2)</t>
+  </si>
+  <si>
+    <t>NEHA YADAV</t>
+  </si>
+  <si>
+    <t>RIYA</t>
+  </si>
+  <si>
+    <t>GARIMA DUDEJA</t>
+  </si>
+  <si>
+    <t>BHUMIKA</t>
   </si>
 </sst>
 </file>
@@ -605,7 +608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -646,6 +649,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -950,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -991,19 +998,19 @@
         <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>79</v>
@@ -1014,7 +1021,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -1026,7 +1033,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>78</v>
@@ -1040,19 +1047,19 @@
         <v>77</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1060,22 +1067,22 @@
         <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>72</v>
+        <v>147</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1083,13 +1090,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>74</v>
@@ -1097,8 +1104,8 @@
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>14</v>
+      <c r="G6" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1106,22 +1113,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1129,22 +1136,22 @@
         <v>24</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>75</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="G8" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1155,19 +1162,19 @@
         <v>76</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1175,19 +1182,19 @@
         <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>13</v>
@@ -1198,22 +1205,22 @@
         <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1221,19 +1228,19 @@
         <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>75</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>16</v>
@@ -1244,22 +1251,22 @@
         <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>76</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1267,7 +1274,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>69</v>
@@ -1279,7 +1286,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>9</v>
@@ -1293,16 +1300,16 @@
         <v>74</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>7</v>
@@ -1313,13 +1320,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>77</v>
@@ -1328,7 +1335,7 @@
         <v>72</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1336,22 +1343,22 @@
         <v>33</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>71</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1362,19 +1369,19 @@
         <v>16</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1385,19 +1392,19 @@
         <v>69</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1405,10 +1412,10 @@
         <v>36</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>77</v>
@@ -1420,7 +1427,7 @@
         <v>75</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1437,13 +1444,13 @@
         <v>69</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1451,22 +1458,22 @@
         <v>38</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>76</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1477,24 +1484,24 @@
         <v>15</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1503,16 +1510,16 @@
         <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1523,19 +1530,19 @@
         <v>73</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>77</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1549,16 +1556,16 @@
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1569,19 +1576,19 @@
         <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="E27" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1595,16 +1602,16 @@
         <v>78</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>99</v>
+      <c r="F28" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1615,19 +1622,19 @@
         <v>9</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="F29" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="G29" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1635,13 +1642,13 @@
         <v>45</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>7</v>
@@ -1650,7 +1657,7 @@
         <v>15</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1658,22 +1665,22 @@
         <v>46</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1684,19 +1691,19 @@
         <v>79</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1704,22 +1711,22 @@
         <v>48</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -1727,22 +1734,22 @@
         <v>49</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>79</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1750,22 +1757,22 @@
         <v>50</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>99</v>
+      <c r="E35" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1773,22 +1780,22 @@
         <v>51</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D36" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="F36" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -1799,19 +1806,19 @@
         <v>13</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -1822,19 +1829,19 @@
         <v>78</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1845,19 +1852,19 @@
         <v>8</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>79</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -1865,22 +1872,22 @@
         <v>55</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1888,22 +1895,22 @@
         <v>56</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1911,22 +1918,22 @@
         <v>68</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>157</v>
+        <v>98</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1934,22 +1941,22 @@
         <v>57</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -1957,22 +1964,22 @@
         <v>66</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1983,16 +1990,16 @@
         <v>75</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>8</v>
@@ -2006,19 +2013,19 @@
         <v>75</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -2026,22 +2033,22 @@
         <v>60</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>142</v>
+        <v>98</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>99</v>
+        <v>135</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2049,22 +2056,22 @@
         <v>67</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>144</v>
+        <v>98</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>99</v>
+        <v>137</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2072,22 +2079,22 @@
         <v>61</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2095,22 +2102,22 @@
         <v>65</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2118,114 +2125,114 @@
         <v>62</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2233,22 +2240,22 @@
         <v>63</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -2256,22 +2263,114 @@
         <v>64</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{478B2D59-E87A-4D18-8954-0A1AD868EE56}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A818F9F9-1790-4EBC-9D98-D53643D1FA62}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="162">
   <si>
     <t>Teacher</t>
   </si>
@@ -420,9 +420,6 @@
     <t>10TH (CS)</t>
   </si>
   <si>
-    <t>9TH (P)</t>
-  </si>
-  <si>
     <t>10TH (P)</t>
   </si>
   <si>
@@ -438,9 +435,6 @@
     <t>11  ARTS+COMM+SCI (IT)</t>
   </si>
   <si>
-    <t>9TH (IT)</t>
-  </si>
-  <si>
     <t>10TH (IT)</t>
   </si>
   <si>
@@ -477,12 +471,6 @@
     <t>12TH ARTS D+F</t>
   </si>
   <si>
-    <t>11TH SCI A(3,4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9TH </t>
-  </si>
-  <si>
     <t>12 TH SCI C</t>
   </si>
   <si>
@@ -504,10 +492,31 @@
     <t>RIYA</t>
   </si>
   <si>
-    <t>GARIMA DUDEJA</t>
-  </si>
-  <si>
     <t>BHUMIKA</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(1,2,3),              9TH A+B+F (4,5,6)</t>
+  </si>
+  <si>
+    <t>9THC+D+E(1,2,3),                             9TH A+B+F (4,5,6)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(4,5,6),              9TH A+B+F (1,2,3)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(4,5,6),               9TH A+B+F (1,2,3)</t>
+  </si>
+  <si>
+    <t>11TH SCI A(3,4),               11TH SCI C+D(1,2)</t>
+  </si>
+  <si>
+    <t>12TH SCI A(5,6),                                    12TH SCI C(5,6)</t>
+  </si>
+  <si>
+    <t>MANISHA</t>
+  </si>
+  <si>
+    <t>11 TH AETS</t>
   </si>
 </sst>
 </file>
@@ -608,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -651,7 +660,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1006,11 +1014,11 @@
       <c r="D2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>71</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>79</v>
@@ -1076,9 +1084,9 @@
         <v>105</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" s="16" t="s">
         <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -1320,10 +1328,10 @@
         <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>86</v>
@@ -1348,14 +1356,14 @@
       <c r="C17" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>71</v>
       </c>
+      <c r="E17" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="F17" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>93</v>
@@ -1392,7 +1400,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>98</v>
@@ -1501,7 +1509,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1668,16 +1676,16 @@
         <v>81</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>71</v>
+        <v>142</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>98</v>
+      <c r="F31" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>98</v>
@@ -1726,7 +1734,7 @@
         <v>98</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -1757,16 +1765,16 @@
         <v>50</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="1" t="s">
         <v>71</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>78</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>113</v>
@@ -1861,7 +1869,7 @@
         <v>98</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>106</v>
@@ -1884,13 +1892,13 @@
         <v>97</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>56</v>
       </c>
@@ -1906,14 +1914,14 @@
       <c r="E41" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>149</v>
+      <c r="F41" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>68</v>
       </c>
@@ -1929,14 +1937,14 @@
       <c r="E42" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>98</v>
+      <c r="F42" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>57</v>
       </c>
@@ -1952,14 +1960,14 @@
       <c r="E43" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>98</v>
+      <c r="F43" s="7" t="s">
+        <v>156</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>66</v>
       </c>
@@ -1970,16 +1978,16 @@
         <v>98</v>
       </c>
       <c r="D44" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="E44" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2028,7 +2036,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>60</v>
       </c>
@@ -2039,16 +2047,16 @@
         <v>98</v>
       </c>
       <c r="D47" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="F47" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2062,16 +2070,16 @@
         <v>98</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2085,10 +2093,10 @@
         <v>92</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>122</v>
@@ -2143,7 +2151,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>117</v>
       </c>
@@ -2159,11 +2167,11 @@
       <c r="E52" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>148</v>
+      <c r="F52" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2282,17 +2290,17 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="16" t="s">
-        <v>155</v>
+      <c r="A58" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>98</v>
@@ -2305,17 +2313,17 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="16" t="s">
-        <v>156</v>
+      <c r="A59" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>98</v>
@@ -2328,20 +2336,20 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="16" t="s">
-        <v>157</v>
+      <c r="A60" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>98</v>
+        <v>161</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>98</v>
@@ -2351,20 +2359,20 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="16" t="s">
-        <v>158</v>
+      <c r="A61" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>98</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96dbc1fdb7cb27ef/Desktop/Substitute-management-v2/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="6_{B5EB076C-04E9-4716-9371-18DE02036C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A818F9F9-1790-4EBC-9D98-D53643D1FA62}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1DDFA4-24BA-49F2-BEAA-08D434045B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="163">
   <si>
     <t>Teacher</t>
   </si>
@@ -66,9 +66,6 @@
     <t>10TH  A</t>
   </si>
   <si>
-    <t xml:space="preserve">11 SCI </t>
-  </si>
-  <si>
     <t>10TH A</t>
   </si>
   <si>
@@ -438,9 +435,6 @@
     <t>10TH (IT)</t>
   </si>
   <si>
-    <t>9TH (PAT)</t>
-  </si>
-  <si>
     <t>10TH (PAT)</t>
   </si>
   <si>
@@ -495,18 +489,6 @@
     <t>BHUMIKA</t>
   </si>
   <si>
-    <t>9TH C+D+E(1,2,3),              9TH A+B+F (4,5,6)</t>
-  </si>
-  <si>
-    <t>9THC+D+E(1,2,3),                             9TH A+B+F (4,5,6)</t>
-  </si>
-  <si>
-    <t>9TH C+D+E(4,5,6),              9TH A+B+F (1,2,3)</t>
-  </si>
-  <si>
-    <t>9TH C+D+E(4,5,6),               9TH A+B+F (1,2,3)</t>
-  </si>
-  <si>
     <t>11TH SCI A(3,4),               11TH SCI C+D(1,2)</t>
   </si>
   <si>
@@ -517,13 +499,34 @@
   </si>
   <si>
     <t>11 TH AETS</t>
+  </si>
+  <si>
+    <t>SH. RAJBIR (DPE)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(IT) (4,5,6),               9TH A+B+F(IT) (1,2,3)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(CS) (4,5,6),              9TH A+B+F(CS) (1,2,3)</t>
+  </si>
+  <si>
+    <t>9THC+D+E(SKT) (1,2,3),                             9TH A+B+F(SKT) (4,5,6)</t>
+  </si>
+  <si>
+    <t>11TH COMM A + 11TH SCI</t>
+  </si>
+  <si>
+    <t>9TH C+D+E (4,5,6),              9TH A+B+F (1,2,3)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(P) (1,2,3),              9TH A+B+F(P) (4,5,6)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,6 +564,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -617,7 +627,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -661,6 +671,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -965,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -1003,298 +1017,298 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>97</v>
+        <v>97</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>96</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="D11" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>9</v>
@@ -1302,22 +1316,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>7</v>
@@ -1325,689 +1339,689 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>7</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F34" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G40" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G42" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D43" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="F43" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G43" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D44" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E44" s="12" t="s">
-        <v>131</v>
-      </c>
       <c r="F44" s="7" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>8</v>
@@ -2015,370 +2029,393 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D47" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="12" t="s">
         <v>132</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>157</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1DDFA4-24BA-49F2-BEAA-08D434045B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D058C809-AFB3-4712-BCE9-D75C9DE75053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -489,37 +489,37 @@
     <t>BHUMIKA</t>
   </si>
   <si>
-    <t>11TH SCI A(3,4),               11TH SCI C+D(1,2)</t>
-  </si>
-  <si>
-    <t>12TH SCI A(5,6),                                    12TH SCI C(5,6)</t>
-  </si>
-  <si>
     <t>MANISHA</t>
   </si>
   <si>
-    <t>11 TH AETS</t>
-  </si>
-  <si>
     <t>SH. RAJBIR (DPE)</t>
   </si>
   <si>
-    <t>9TH C+D+E(IT) (4,5,6),               9TH A+B+F(IT) (1,2,3)</t>
-  </si>
-  <si>
-    <t>9TH C+D+E(CS) (4,5,6),              9TH A+B+F(CS) (1,2,3)</t>
-  </si>
-  <si>
-    <t>9THC+D+E(SKT) (1,2,3),                             9TH A+B+F(SKT) (4,5,6)</t>
-  </si>
-  <si>
     <t>11TH COMM A + 11TH SCI</t>
   </si>
   <si>
-    <t>9TH C+D+E (4,5,6),              9TH A+B+F (1,2,3)</t>
-  </si>
-  <si>
-    <t>9TH C+D+E(P) (1,2,3),              9TH A+B+F(P) (4,5,6)</t>
+    <t>11TH SCI A(3,4)                11TH SCI C+D(1,2)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(4,5,6)               9TH A+B+F(1,2,3)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(CS)(4,5,6)              9TH A+B+F(CS)(1,2,3)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(P)(1,2,3)             9TH A+B+F(P)(4,5,6)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(IT)(4,5,6)               9TH A+B+F(IT)(1,2,3)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E(SKT)(1,2,3)                             9TH A+B+F(SKT)(4,5,6)</t>
+  </si>
+  <si>
+    <t>12TH SCI A(5,6)                                     12TH SCI C(5,6)</t>
+  </si>
+  <si>
+    <t>11 TH ARTS</t>
   </si>
 </sst>
 </file>
@@ -627,7 +627,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -673,7 +673,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1146,7 +1145,7 @@
       <c r="E7" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>96</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1213,7 +1212,7 @@
         <v>87</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>97</v>
@@ -1929,7 +1928,7 @@
         <v>103</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>128</v>
@@ -1952,7 +1951,7 @@
         <v>123</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>124</v>
@@ -1975,7 +1974,7 @@
         <v>126</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>127</v>
@@ -1998,7 +1997,7 @@
         <v>130</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>16</v>
@@ -2067,7 +2066,7 @@
         <v>132</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>133</v>
@@ -2182,10 +2181,10 @@
         <v>97</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2311,7 +2310,7 @@
         <v>97</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>8</v>
@@ -2351,7 +2350,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>97</v>
@@ -2363,7 +2362,7 @@
         <v>97</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>97</v>
@@ -2396,8 +2395,8 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="17" t="s">
-        <v>156</v>
+      <c r="A62" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>97</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D058C809-AFB3-4712-BCE9-D75C9DE75053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAFDEFD-ABDE-4CEC-857F-06F76E4FDF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,22 +504,22 @@
     <t>9TH C+D+E(4,5,6)               9TH A+B+F(1,2,3)</t>
   </si>
   <si>
-    <t>9TH C+D+E(CS)(4,5,6)              9TH A+B+F(CS)(1,2,3)</t>
-  </si>
-  <si>
-    <t>9TH C+D+E(P)(1,2,3)             9TH A+B+F(P)(4,5,6)</t>
-  </si>
-  <si>
-    <t>9TH C+D+E(IT)(4,5,6)               9TH A+B+F(IT)(1,2,3)</t>
-  </si>
-  <si>
-    <t>9TH C+D+E(SKT)(1,2,3)                             9TH A+B+F(SKT)(4,5,6)</t>
-  </si>
-  <si>
     <t>12TH SCI A(5,6)                                     12TH SCI C(5,6)</t>
   </si>
   <si>
     <t>11 TH ARTS</t>
+  </si>
+  <si>
+    <t>9TH C+D+E IT(4,5,6)               9TH A+B+F IT(1,2,3)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E CS(4,5,6)              9TH A+B+F CS(1,2,3)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E SKT(1,2,3)                             9TH A+B+F SKT(4,5,6)</t>
+  </si>
+  <si>
+    <t>9TH C+D+E P(1,2,3)             9TH A+B+F P(4,5,6)</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1928,7 @@
         <v>103</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>128</v>
@@ -1951,7 +1951,7 @@
         <v>123</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>124</v>
@@ -1974,7 +1974,7 @@
         <v>126</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>127</v>
@@ -2184,7 +2184,7 @@
         <v>155</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2362,7 +2362,7 @@
         <v>97</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>97</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAFDEFD-ABDE-4CEC-857F-06F76E4FDF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBACB40-AFB7-4748-A54E-B7D53BC5DBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,9 +507,6 @@
     <t>12TH SCI A(5,6)                                     12TH SCI C(5,6)</t>
   </si>
   <si>
-    <t>11 TH ARTS</t>
-  </si>
-  <si>
     <t>9TH C+D+E IT(4,5,6)               9TH A+B+F IT(1,2,3)</t>
   </si>
   <si>
@@ -520,6 +517,9 @@
   </si>
   <si>
     <t>9TH C+D+E P(1,2,3)             9TH A+B+F P(4,5,6)</t>
+  </si>
+  <si>
+    <t>9TH</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1928,7 @@
         <v>103</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>128</v>
@@ -1951,7 +1951,7 @@
         <v>123</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>124</v>
@@ -1974,7 +1974,7 @@
         <v>126</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>127</v>
@@ -2066,7 +2066,7 @@
         <v>132</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>133</v>
@@ -2310,13 +2310,13 @@
         <v>97</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>97</v>
@@ -2339,7 +2339,7 @@
         <v>12</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>97</v>
@@ -2362,10 +2362,10 @@
         <v>97</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>97</v>
@@ -2376,7 +2376,7 @@
         <v>151</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>8</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBACB40-AFB7-4748-A54E-B7D53BC5DBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDF8293-249C-4D4E-9A59-B4B61DCEFBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1827,7 +1827,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>79</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Substitute-management-v2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDF8293-249C-4D4E-9A59-B4B61DCEFBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B83538-1A63-4FFE-98AD-F3B6F2C5A2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2026,7 +2026,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>58</v>
       </c>
